--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484607_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484607_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.648</v>
+        <v>6.0325</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8488</v>
+        <v>3.5306</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7992</v>
+        <v>2.5019</v>
       </c>
       <c r="G2" t="n">
         <v>1.4006</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3757</v>
+        <v>1.7602</v>
       </c>
       <c r="T2" t="n">
-        <v>2.488</v>
+        <v>1.1697</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8877</v>
+        <v>0.5904</v>
       </c>
       <c r="V2" t="n">
         <v>1.5889</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9349</v>
+        <v>3.835</v>
       </c>
       <c r="E3" t="n">
-        <v>1.345</v>
+        <v>1.8397</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5899</v>
+        <v>1.9953</v>
       </c>
       <c r="G3" t="n">
         <v>2.3961</v>
@@ -688,13 +688,13 @@
         <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5779</v>
+        <v>0.4781</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6621</v>
+        <v>-0.1674</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2401</v>
+        <v>0.6455</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3219</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0181</v>
+        <v>2.3249</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0982</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.92</v>
+        <v>1.3718</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3019</v>
+        <v>-0.0067</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0646</v>
+        <v>1.1058</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2373</v>
+        <v>-1.1125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2935</v>
+        <v>0.1586</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2102</v>
+        <v>1.399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0833</v>
+        <v>-1.2404</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5955</v>
+        <v>-0.1653</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2748</v>
+        <v>-0.2932</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3207</v>
+        <v>0.1279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1472</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4827</v>
+        <v>0.1218</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6645</v>
+        <v>-0.1122</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6231</v>
+        <v>1.5889</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4997</v>
+        <v>2.2681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4995</v>
+        <v>2.271</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0002</v>
+        <v>-0.0029</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0067</v>
+        <v>1.0162</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1058</v>
+        <v>0.1697</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1125</v>
+        <v>0.8465</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1586</v>
+        <v>2.5505</v>
       </c>
       <c r="K5" t="n">
-        <v>1.399</v>
+        <v>1.223</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2404</v>
+        <v>1.3275</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1653</v>
+        <v>-1.5342</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2932</v>
+        <v>-1.0532</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1279</v>
+        <v>-0.481</v>
       </c>
       <c r="P5" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8156</v>
+        <v>0.4351</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3318</v>
+        <v>0.3149</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4838</v>
+        <v>0.1203</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5889</v>
+        <v>0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2431</v>
+        <v>2.007</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2955</v>
+        <v>1.1366</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0524</v>
+        <v>0.8704</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0162</v>
+        <v>-0.3019</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1697</v>
+        <v>-0.0646</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8465</v>
+        <v>-0.2373</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5505</v>
+        <v>0.2935</v>
       </c>
       <c r="K6" t="n">
-        <v>1.223</v>
+        <v>0.2102</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3275</v>
+        <v>0.0833</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5342</v>
+        <v>-0.5955</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0532</v>
+        <v>-0.2748</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.481</v>
+        <v>-0.3207</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5899</v>
+        <v>1.1361</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6606</v>
+        <v>0.5211</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0707</v>
+        <v>0.615</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6335</v>
+        <v>0.6231</v>
       </c>
       <c r="W6" t="n">
         <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3115</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>B. BREM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6502</v>
+        <v>1.7262</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6502</v>
+        <v>0.7879</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.9383</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6502</v>
+        <v>0.4559</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6502</v>
+        <v>1.9304</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.4745</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6502</v>
+        <v>0.1051</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6502</v>
+        <v>1.3872</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.2821</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.3508</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.5433</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.1925</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.2153</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3609</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.1456</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. BREM</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6458</v>
+        <v>1.0165</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0047</v>
+        <v>1.1852</v>
       </c>
       <c r="F8" t="n">
-        <v>0.641</v>
+        <v>-0.1688</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4559</v>
+        <v>2.0239</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9304</v>
+        <v>1.2964</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4745</v>
+        <v>0.7276</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1051</v>
+        <v>3.5218</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3872</v>
+        <v>2.1208</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2821</v>
+        <v>1.401</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3508</v>
+        <v>-1.4979</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5433</v>
+        <v>-0.8244</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1925</v>
+        <v>-0.6735</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8652</v>
+        <v>0.9717</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4223</v>
+        <v>0.3914</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4428</v>
+        <v>0.5803</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3219</v>
+        <v>-1.2461</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0.0208</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5777</v>
+        <v>0.6502</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.726</v>
+        <v>0.6502</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3037</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.163</v>
+        <v>0.6502</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4206</v>
+        <v>0.6502</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5836</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2237</v>
+        <v>0.6502</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0249</v>
+        <v>0.6502</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1987</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0606</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4456</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3849</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3351</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4193</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0843</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1616</v>
+        <v>0.5177</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4113</v>
+        <v>-0.9594</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5729</v>
+        <v>1.4772</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2518</v>
+        <v>-1.163</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1557</v>
+        <v>0.4206</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0961</v>
+        <v>-1.5836</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7803</v>
+        <v>-1.2237</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7803</v>
+        <v>-0.0249</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.1987</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4715</v>
+        <v>0.0606</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3754</v>
+        <v>0.4456</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0961</v>
+        <v>-0.3849</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1738</v>
+        <v>0.2751</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2753</v>
+        <v>0.1859</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1014</v>
+        <v>0.0892</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2148</v>
+        <v>0.2855</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0035</v>
+        <v>-0.4113</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2183</v>
+        <v>0.6968</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0239</v>
+        <v>1.2518</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2964</v>
+        <v>1.1557</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7276</v>
+        <v>0.0961</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5218</v>
+        <v>0.7803</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1208</v>
+        <v>0.7803</v>
       </c>
       <c r="L11" t="n">
-        <v>1.401</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4979</v>
+        <v>0.4715</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8244</v>
+        <v>0.3754</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6735</v>
+        <v>0.0961</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2596</v>
+        <v>-0.05</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7903</v>
+        <v>-0.2753</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.2253</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2461</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7082</v>
+        <v>-3.1066</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3605</v>
+        <v>-3.6351</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6523</v>
+        <v>0.5284</v>
       </c>
       <c r="G12" t="n">
         <v>-4.4652</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9506</v>
+        <v>1.5522</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2074</v>
+        <v>0.9329</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7432</v>
+        <v>0.6193</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0104</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4561</v>
+        <v>17.557</v>
       </c>
       <c r="E13" t="n">
-        <v>6.247599999999998</v>
+        <v>7.3485</v>
       </c>
       <c r="F13" t="n">
-        <v>10.2085</v>
+        <v>10.2084</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2579</v>
+        <v>3.257899999999999</v>
       </c>
       <c r="H13" t="n">
         <v>7.5859</v>
@@ -1459,7 +1459,7 @@
         <v>-3.0476</v>
       </c>
       <c r="P13" t="n">
-        <v>2.748799999999999</v>
+        <v>2.7488</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.0793</v>
@@ -1468,16 +1468,16 @@
         <v>12.8279</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6824</v>
+        <v>6.7834</v>
       </c>
       <c r="T13" t="n">
-        <v>2.455</v>
+        <v>3.5559</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2274</v>
+        <v>3.2275</v>
       </c>
       <c r="V13" t="n">
-        <v>4.766799999999999</v>
+        <v>4.7668</v>
       </c>
       <c r="W13" t="n">
         <v>5.7637</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9938</v>
+        <v>2.4557</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1059</v>
+        <v>3.3943</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1121</v>
+        <v>-0.9387</v>
       </c>
       <c r="G14" t="n">
         <v>1.4467</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3142</v>
+        <v>-0.8524</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8627</v>
+        <v>-0.5743</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4515</v>
+        <v>-0.2781</v>
       </c>
       <c r="V14" t="n">
         <v>0.945</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0346</v>
+        <v>0.0594</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1101</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1447</v>
+        <v>0.1695</v>
       </c>
       <c r="G15" t="n">
         <v>0.1282</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0936</v>
+        <v>-0.0688</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0278</v>
+        <v>0.048</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1791</v>
+        <v>0.9706</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2069</v>
+        <v>-0.9226</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9356</v>
+        <v>0.4484</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1024</v>
+        <v>-1.1833</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.6317</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8489</v>
+        <v>1.4619</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0154</v>
+        <v>0.0867</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8335</v>
+        <v>1.3753</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9133</v>
+        <v>-1.0136</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.913</v>
+        <v>-1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0003</v>
+        <v>0.2564</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.9321</v>
+        <v>0.5498</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5814</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5027</v>
+        <v>-0.6282</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2678</v>
+        <v>-0.4913</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2349</v>
+        <v>-0.1369</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5339</v>
+        <v>-0.3219</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.1778</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1968</v>
+        <v>-1.0321</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.4979</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0713</v>
+        <v>-1.5301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4484</v>
+        <v>0.5787</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1833</v>
+        <v>0.6267</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6317</v>
+        <v>-0.048</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4619</v>
+        <v>1.7956</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0867</v>
+        <v>1.619</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3753</v>
+        <v>0.1765</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0136</v>
+        <v>-1.2169</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.27</v>
+        <v>-0.9923</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2564</v>
+        <v>-0.2246</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.873</v>
+        <v>-1.0219</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5875</v>
+        <v>-0.3918</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2855</v>
+        <v>-0.6301</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3219</v>
+        <v>-0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9273</v>
+        <v>-1.7617</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9787</v>
+        <v>-0.2362</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.906</v>
+        <v>-1.5255</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5787</v>
+        <v>-0.7388</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6267</v>
+        <v>-2.3482</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.048</v>
+        <v>1.6094</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7956</v>
+        <v>1.3283</v>
       </c>
       <c r="K18" t="n">
-        <v>1.619</v>
+        <v>-0.666</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1765</v>
+        <v>1.9943</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2169</v>
+        <v>-2.0671</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9923</v>
+        <v>-1.6822</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2246</v>
+        <v>-0.3849</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.917</v>
+        <v>-0.701</v>
       </c>
       <c r="T18" t="n">
-        <v>0.089</v>
+        <v>-0.3367</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0061</v>
+        <v>-0.3643</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9554</v>
+        <v>-0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0104</v>
+        <v>-0.3115</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9658</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>-2.1228</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-2.475</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.9356</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.1024</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8489</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.0154</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8335</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.9133</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.913</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-2.9321</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4.5814</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.6493</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.0332</v>
+      </c>
+      <c r="V19" t="n">
         <v>-2.5339</v>
       </c>
-      <c r="E19" t="n">
-        <v>-0.9093</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-1.6246</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.7388</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-2.3482</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6094</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.3283</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.666</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.9943</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-2.0671</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-1.6822</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.3849</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-0.9163</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.9163</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.4731</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-1.0098</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.4634</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.3219</v>
-      </c>
       <c r="W19" t="n">
-        <v>-0.3115</v>
+        <v>0.6439</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0104</v>
+        <v>-3.1778</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8502</v>
+        <v>-2.6301</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4764</v>
+        <v>-1.3802</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3738</v>
+        <v>-1.2499</v>
       </c>
       <c r="G20" t="n">
         <v>1.2409</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4679</v>
+        <v>-0.2479</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2586</v>
+        <v>-0.1625</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2093</v>
+        <v>-0.0854</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5235</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1703</v>
+        <v>-2.9543</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5681</v>
+        <v>-3.4139</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3978</v>
+        <v>0.4596</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.5457</v>
+        <v>-1.3185</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1002</v>
+        <v>-1.5301</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4456</v>
+        <v>0.2116</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.4768</v>
+        <v>-1.0161</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6787</v>
+        <v>-0.4584</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7981</v>
+        <v>-0.5577</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0689</v>
+        <v>-0.3024</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4214</v>
+        <v>-1.0716</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3525</v>
+        <v>0.7692</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.313</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.497</v>
+        <v>-0.5652</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1839</v>
+        <v>-0.3375</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7119</v>
+        <v>-3.1689</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8947</v>
+        <v>-4.4719</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1828</v>
+        <v>1.303</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3185</v>
+        <v>-3.5457</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5301</v>
+        <v>-2.1002</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2116</v>
+        <v>-1.4456</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0161</v>
+        <v>-3.4768</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4584</v>
+        <v>-1.6787</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5577</v>
+        <v>-1.7981</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3024</v>
+        <v>-0.0689</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0716</v>
+        <v>-0.4214</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7692</v>
+        <v>0.3525</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6603</v>
+        <v>-0.3116</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.046</v>
+        <v>-0.4008</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6143</v>
+        <v>0.0892</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0664</v>
+        <v>-4.7081</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3882</v>
+        <v>-5.8112</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3218</v>
+        <v>1.1032</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4333</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0729</v>
+        <v>-0.7146</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2126</v>
+        <v>-0.6357</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1398</v>
+        <v>-0.0789</v>
       </c>
       <c r="V23" t="n">
         <v>0.6231</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.4562</v>
+        <v>-15.8149</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.2086</v>
+        <v>-10.2085</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.247599999999998</v>
+        <v>-5.6065</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2578</v>
@@ -2296,16 +2296,16 @@
         <v>-7.586</v>
       </c>
       <c r="I24" t="n">
-        <v>4.328099999999999</v>
+        <v>4.3281</v>
       </c>
       <c r="J24" t="n">
-        <v>4.8499</v>
+        <v>4.849900000000002</v>
       </c>
       <c r="K24" t="n">
         <v>1.8024</v>
       </c>
       <c r="L24" t="n">
-        <v>3.047400000000001</v>
+        <v>3.0474</v>
       </c>
       <c r="M24" t="n">
         <v>-8.107800000000001</v>
@@ -2326,13 +2326,13 @@
         <v>10.0791</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.682300000000001</v>
+        <v>-5.0415</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.2275</v>
+        <v>-3.227599999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.455</v>
+        <v>-1.8139</v>
       </c>
       <c r="V24" t="n">
         <v>-4.7666</v>
@@ -2341,7 +2341,7 @@
         <v>0.9970999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.763599999999999</v>
+        <v>-5.7636</v>
       </c>
     </row>
   </sheetData>
